--- a/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 500 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-08 14:48:49</t>
+          <t>Comprehensive 500 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>✅ PASSING</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2524,12 +2524,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3174,12 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4224,12 +4224,12 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -4974,12 +4974,12 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5074,12 +5074,12 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5124,12 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5374,12 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5724,12 +5724,12 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6024,12 +6024,12 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6174,12 +6174,12 @@
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6474,12 +6474,12 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6724,12 +6724,12 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6774,12 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6924,12 +6924,12 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7474,12 +7474,12 @@
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7524,12 +7524,12 @@
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7774,12 @@
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7824,12 +7824,12 @@
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7924,12 +7924,12 @@
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8074,12 +8074,12 @@
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8374,12 +8374,12 @@
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8424,12 +8424,12 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8524,12 @@
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8574,12 @@
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8674,12 @@
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8824,12 +8824,12 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8874,12 +8874,12 @@
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8974,12 @@
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9124,12 +9124,12 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9174,12 +9174,12 @@
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9424,12 +9424,12 @@
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9474,12 +9474,12 @@
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9574,12 +9574,12 @@
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9724,12 +9724,12 @@
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9774,12 +9774,12 @@
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9874,12 @@
       </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9924,12 +9924,12 @@
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10024,12 +10024,12 @@
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10174,12 @@
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10224,12 +10224,12 @@
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="I183" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10374,12 +10374,12 @@
       </c>
       <c r="I185" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10624,12 +10624,12 @@
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="I191" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10774,12 +10774,12 @@
       </c>
       <c r="I193" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10824,12 +10824,12 @@
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="I197" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11024,12 +11024,12 @@
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11074,12 +11074,12 @@
       </c>
       <c r="I199" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="I201" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11274,12 +11274,12 @@
       </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11324,12 +11324,12 @@
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11374,12 +11374,12 @@
       </c>
       <c r="I205" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11474,12 +11474,12 @@
       </c>
       <c r="I207" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11574,12 +11574,12 @@
       </c>
       <c r="I209" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11674,12 +11674,12 @@
       </c>
       <c r="I211" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11724,12 +11724,12 @@
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11774,12 +11774,12 @@
       </c>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11824,12 +11824,12 @@
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="I215" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11924,12 +11924,12 @@
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -11974,12 +11974,12 @@
       </c>
       <c r="I217" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12024,12 +12024,12 @@
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12174,12 +12174,12 @@
       </c>
       <c r="I221" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12274,12 +12274,12 @@
       </c>
       <c r="I223" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="I225" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12424,12 +12424,12 @@
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12474,12 +12474,12 @@
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12524,12 +12524,12 @@
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12574,12 +12574,12 @@
       </c>
       <c r="I229" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12624,12 +12624,12 @@
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="I231" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12724,12 +12724,12 @@
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="I233" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12824,12 +12824,12 @@
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12874,12 +12874,12 @@
       </c>
       <c r="I235" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -12974,12 +12974,12 @@
       </c>
       <c r="I237" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13024,12 +13024,12 @@
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13074,12 +13074,12 @@
       </c>
       <c r="I239" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="I241" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13224,12 +13224,12 @@
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13274,12 +13274,12 @@
       </c>
       <c r="I243" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13324,12 +13324,12 @@
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13374,12 +13374,12 @@
       </c>
       <c r="I245" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13424,12 +13424,12 @@
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13474,12 +13474,12 @@
       </c>
       <c r="I247" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13524,12 +13524,12 @@
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13574,12 +13574,12 @@
       </c>
       <c r="I249" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13624,12 +13624,12 @@
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13724,12 +13724,12 @@
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13774,12 +13774,12 @@
       </c>
       <c r="I253" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13824,12 +13824,12 @@
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13874,12 +13874,12 @@
       </c>
       <c r="I255" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13924,12 +13924,12 @@
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I257" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14024,12 +14024,12 @@
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I259" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14124,12 +14124,12 @@
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14174,12 +14174,12 @@
       </c>
       <c r="I261" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14224,12 +14224,12 @@
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14274,12 +14274,12 @@
       </c>
       <c r="I263" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14324,12 +14324,12 @@
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="I265" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14424,12 +14424,12 @@
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="I267" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14524,12 +14524,12 @@
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14574,12 +14574,12 @@
       </c>
       <c r="I269" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14624,12 +14624,12 @@
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14674,12 +14674,12 @@
       </c>
       <c r="I271" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14724,12 +14724,12 @@
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14774,12 +14774,12 @@
       </c>
       <c r="I273" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14824,12 +14824,12 @@
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14874,12 +14874,12 @@
       </c>
       <c r="I275" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14924,12 +14924,12 @@
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -14974,12 +14974,12 @@
       </c>
       <c r="I277" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15024,12 +15024,12 @@
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15074,12 +15074,12 @@
       </c>
       <c r="I279" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15174,12 +15174,12 @@
       </c>
       <c r="I281" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15224,12 +15224,12 @@
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15274,12 +15274,12 @@
       </c>
       <c r="I283" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15324,12 +15324,12 @@
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15374,12 +15374,12 @@
       </c>
       <c r="I285" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15424,12 +15424,12 @@
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="I287" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15524,12 +15524,12 @@
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="I289" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15624,12 +15624,12 @@
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15674,12 +15674,12 @@
       </c>
       <c r="I291" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15724,12 +15724,12 @@
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15774,12 +15774,12 @@
       </c>
       <c r="I293" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15824,12 +15824,12 @@
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15874,12 +15874,12 @@
       </c>
       <c r="I295" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15924,12 +15924,12 @@
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -15974,12 +15974,12 @@
       </c>
       <c r="I297" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16024,12 +16024,12 @@
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16074,12 +16074,12 @@
       </c>
       <c r="I299" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16124,12 +16124,12 @@
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16174,12 +16174,12 @@
       </c>
       <c r="I301" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16274,12 +16274,12 @@
       </c>
       <c r="I303" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J303" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16324,12 +16324,12 @@
       </c>
       <c r="I304" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J304" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16374,12 +16374,12 @@
       </c>
       <c r="I305" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J305" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16424,12 +16424,12 @@
       </c>
       <c r="I306" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J306" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16474,12 +16474,12 @@
       </c>
       <c r="I307" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J307" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16524,12 +16524,12 @@
       </c>
       <c r="I308" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J308" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16574,12 +16574,12 @@
       </c>
       <c r="I309" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J309" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16624,12 +16624,12 @@
       </c>
       <c r="I310" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J310" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16674,12 +16674,12 @@
       </c>
       <c r="I311" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J311" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16724,12 +16724,12 @@
       </c>
       <c r="I312" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J312" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16774,12 @@
       </c>
       <c r="I313" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J313" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16824,12 +16824,12 @@
       </c>
       <c r="I314" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J314" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16874,12 +16874,12 @@
       </c>
       <c r="I315" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J315" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16924,12 +16924,12 @@
       </c>
       <c r="I316" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J316" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -16974,12 +16974,12 @@
       </c>
       <c r="I317" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J317" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="I318" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J318" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17074,12 +17074,12 @@
       </c>
       <c r="I319" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J319" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17124,12 +17124,12 @@
       </c>
       <c r="I320" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J320" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="I321" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J321" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17224,12 +17224,12 @@
       </c>
       <c r="I322" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J322" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17274,12 +17274,12 @@
       </c>
       <c r="I323" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J323" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17324,12 +17324,12 @@
       </c>
       <c r="I324" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J324" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17374,12 +17374,12 @@
       </c>
       <c r="I325" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J325" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17424,12 +17424,12 @@
       </c>
       <c r="I326" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J326" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17474,12 +17474,12 @@
       </c>
       <c r="I327" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J327" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17524,12 +17524,12 @@
       </c>
       <c r="I328" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J328" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17574,12 +17574,12 @@
       </c>
       <c r="I329" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J329" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17624,12 +17624,12 @@
       </c>
       <c r="I330" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J330" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17674,12 +17674,12 @@
       </c>
       <c r="I331" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J331" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17724,12 +17724,12 @@
       </c>
       <c r="I332" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J332" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17774,12 +17774,12 @@
       </c>
       <c r="I333" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J333" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17824,12 +17824,12 @@
       </c>
       <c r="I334" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J334" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17874,12 +17874,12 @@
       </c>
       <c r="I335" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J335" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17924,12 +17924,12 @@
       </c>
       <c r="I336" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J336" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -17974,12 +17974,12 @@
       </c>
       <c r="I337" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J337" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="I338" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J338" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18074,12 +18074,12 @@
       </c>
       <c r="I339" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J339" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18124,12 +18124,12 @@
       </c>
       <c r="I340" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J340" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18174,12 +18174,12 @@
       </c>
       <c r="I341" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J341" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18224,12 +18224,12 @@
       </c>
       <c r="I342" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J342" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18274,12 +18274,12 @@
       </c>
       <c r="I343" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J343" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18324,12 +18324,12 @@
       </c>
       <c r="I344" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J344" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18374,12 +18374,12 @@
       </c>
       <c r="I345" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J345" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18424,12 +18424,12 @@
       </c>
       <c r="I346" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J346" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18474,12 +18474,12 @@
       </c>
       <c r="I347" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J347" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18524,12 +18524,12 @@
       </c>
       <c r="I348" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J348" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18574,12 +18574,12 @@
       </c>
       <c r="I349" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J349" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18624,12 +18624,12 @@
       </c>
       <c r="I350" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J350" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18674,12 +18674,12 @@
       </c>
       <c r="I351" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J351" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18724,12 +18724,12 @@
       </c>
       <c r="I352" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J352" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18774,12 +18774,12 @@
       </c>
       <c r="I353" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J353" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18824,12 +18824,12 @@
       </c>
       <c r="I354" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J354" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18874,12 +18874,12 @@
       </c>
       <c r="I355" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J355" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18924,12 +18924,12 @@
       </c>
       <c r="I356" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J356" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -18974,12 +18974,12 @@
       </c>
       <c r="I357" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J357" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19024,12 +19024,12 @@
       </c>
       <c r="I358" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J358" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19074,12 +19074,12 @@
       </c>
       <c r="I359" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J359" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19124,12 +19124,12 @@
       </c>
       <c r="I360" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J360" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19174,12 +19174,12 @@
       </c>
       <c r="I361" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J361" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19224,12 +19224,12 @@
       </c>
       <c r="I362" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J362" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19274,12 +19274,12 @@
       </c>
       <c r="I363" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J363" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19324,12 +19324,12 @@
       </c>
       <c r="I364" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J364" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19374,12 +19374,12 @@
       </c>
       <c r="I365" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J365" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I366" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J366" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19474,12 +19474,12 @@
       </c>
       <c r="I367" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J367" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19524,12 +19524,12 @@
       </c>
       <c r="I368" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J368" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19574,12 +19574,12 @@
       </c>
       <c r="I369" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J369" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19624,12 +19624,12 @@
       </c>
       <c r="I370" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J370" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="I371" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J371" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19724,12 +19724,12 @@
       </c>
       <c r="I372" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J372" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19774,12 +19774,12 @@
       </c>
       <c r="I373" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J373" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19824,12 +19824,12 @@
       </c>
       <c r="I374" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J374" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19874,12 +19874,12 @@
       </c>
       <c r="I375" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J375" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19924,12 +19924,12 @@
       </c>
       <c r="I376" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J376" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -19974,12 +19974,12 @@
       </c>
       <c r="I377" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J377" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20024,12 +20024,12 @@
       </c>
       <c r="I378" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J378" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20074,12 +20074,12 @@
       </c>
       <c r="I379" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J379" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20124,12 +20124,12 @@
       </c>
       <c r="I380" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J380" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20174,12 +20174,12 @@
       </c>
       <c r="I381" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J381" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20224,12 +20224,12 @@
       </c>
       <c r="I382" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J382" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20274,12 +20274,12 @@
       </c>
       <c r="I383" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J383" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20324,12 +20324,12 @@
       </c>
       <c r="I384" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J384" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20374,12 @@
       </c>
       <c r="I385" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J385" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20424,12 +20424,12 @@
       </c>
       <c r="I386" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J386" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20474,12 +20474,12 @@
       </c>
       <c r="I387" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J387" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20524,12 +20524,12 @@
       </c>
       <c r="I388" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J388" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20574,12 +20574,12 @@
       </c>
       <c r="I389" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J389" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20624,12 +20624,12 @@
       </c>
       <c r="I390" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J390" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20674,12 +20674,12 @@
       </c>
       <c r="I391" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J391" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20724,12 +20724,12 @@
       </c>
       <c r="I392" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J392" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20774,12 +20774,12 @@
       </c>
       <c r="I393" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J393" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20824,12 +20824,12 @@
       </c>
       <c r="I394" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J394" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20874,12 +20874,12 @@
       </c>
       <c r="I395" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J395" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20924,12 +20924,12 @@
       </c>
       <c r="I396" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J396" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -20974,12 +20974,12 @@
       </c>
       <c r="I397" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J397" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21024,12 +21024,12 @@
       </c>
       <c r="I398" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J398" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21074,12 +21074,12 @@
       </c>
       <c r="I399" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J399" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21124,12 +21124,12 @@
       </c>
       <c r="I400" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J400" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21174,12 +21174,12 @@
       </c>
       <c r="I401" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J401" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21224,12 +21224,12 @@
       </c>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J402" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21274,12 +21274,12 @@
       </c>
       <c r="I403" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J403" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21324,12 +21324,12 @@
       </c>
       <c r="I404" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J404" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21374,12 +21374,12 @@
       </c>
       <c r="I405" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J405" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21424,12 +21424,12 @@
       </c>
       <c r="I406" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J406" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21474,12 +21474,12 @@
       </c>
       <c r="I407" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J407" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21524,12 +21524,12 @@
       </c>
       <c r="I408" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J408" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21574,12 +21574,12 @@
       </c>
       <c r="I409" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J409" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21624,12 +21624,12 @@
       </c>
       <c r="I410" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J410" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21674,12 +21674,12 @@
       </c>
       <c r="I411" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J411" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21724,12 +21724,12 @@
       </c>
       <c r="I412" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J412" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21774,12 +21774,12 @@
       </c>
       <c r="I413" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J413" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21824,12 +21824,12 @@
       </c>
       <c r="I414" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J414" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21874,12 +21874,12 @@
       </c>
       <c r="I415" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J415" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21924,12 +21924,12 @@
       </c>
       <c r="I416" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J416" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -21974,12 +21974,12 @@
       </c>
       <c r="I417" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J417" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22024,12 +22024,12 @@
       </c>
       <c r="I418" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J418" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22074,12 +22074,12 @@
       </c>
       <c r="I419" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J419" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22124,12 +22124,12 @@
       </c>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J420" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22174,12 +22174,12 @@
       </c>
       <c r="I421" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J421" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22224,12 +22224,12 @@
       </c>
       <c r="I422" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J422" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22274,12 +22274,12 @@
       </c>
       <c r="I423" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J423" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22324,12 +22324,12 @@
       </c>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J424" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22374,12 +22374,12 @@
       </c>
       <c r="I425" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J425" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22424,12 +22424,12 @@
       </c>
       <c r="I426" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J426" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22474,12 +22474,12 @@
       </c>
       <c r="I427" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J427" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22524,12 +22524,12 @@
       </c>
       <c r="I428" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J428" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22574,12 +22574,12 @@
       </c>
       <c r="I429" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J429" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22624,12 +22624,12 @@
       </c>
       <c r="I430" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J430" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22674,12 +22674,12 @@
       </c>
       <c r="I431" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J431" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22724,12 +22724,12 @@
       </c>
       <c r="I432" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J432" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22774,12 +22774,12 @@
       </c>
       <c r="I433" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J433" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22824,12 +22824,12 @@
       </c>
       <c r="I434" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J434" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22874,12 +22874,12 @@
       </c>
       <c r="I435" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J435" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22924,12 +22924,12 @@
       </c>
       <c r="I436" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J436" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -22974,12 +22974,12 @@
       </c>
       <c r="I437" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J437" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="I438" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J438" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23074,12 +23074,12 @@
       </c>
       <c r="I439" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J439" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="I440" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J440" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23174,12 +23174,12 @@
       </c>
       <c r="I441" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J441" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23224,12 +23224,12 @@
       </c>
       <c r="I442" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J442" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23274,12 +23274,12 @@
       </c>
       <c r="I443" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J443" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23324,12 +23324,12 @@
       </c>
       <c r="I444" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J444" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23374,12 @@
       </c>
       <c r="I445" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J445" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23424,12 +23424,12 @@
       </c>
       <c r="I446" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J446" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23474,12 +23474,12 @@
       </c>
       <c r="I447" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J447" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23524,12 +23524,12 @@
       </c>
       <c r="I448" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J448" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23574,12 +23574,12 @@
       </c>
       <c r="I449" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J449" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23624,12 +23624,12 @@
       </c>
       <c r="I450" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J450" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23674,12 +23674,12 @@
       </c>
       <c r="I451" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J451" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23724,12 +23724,12 @@
       </c>
       <c r="I452" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J452" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23774,12 +23774,12 @@
       </c>
       <c r="I453" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J453" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23824,12 +23824,12 @@
       </c>
       <c r="I454" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J454" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23874,12 +23874,12 @@
       </c>
       <c r="I455" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J455" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23924,12 +23924,12 @@
       </c>
       <c r="I456" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J456" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -23974,12 +23974,12 @@
       </c>
       <c r="I457" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J457" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24024,12 +24024,12 @@
       </c>
       <c r="I458" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J458" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24074,12 +24074,12 @@
       </c>
       <c r="I459" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J459" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24124,12 +24124,12 @@
       </c>
       <c r="I460" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J460" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24174,12 +24174,12 @@
       </c>
       <c r="I461" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J461" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24224,12 +24224,12 @@
       </c>
       <c r="I462" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J462" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24274,12 +24274,12 @@
       </c>
       <c r="I463" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J463" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24324,12 +24324,12 @@
       </c>
       <c r="I464" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J464" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24374,12 +24374,12 @@
       </c>
       <c r="I465" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J465" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24424,12 +24424,12 @@
       </c>
       <c r="I466" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J466" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24474,12 +24474,12 @@
       </c>
       <c r="I467" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J467" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24524,12 +24524,12 @@
       </c>
       <c r="I468" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J468" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24574,12 +24574,12 @@
       </c>
       <c r="I469" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J469" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24624,12 +24624,12 @@
       </c>
       <c r="I470" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J470" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24674,12 +24674,12 @@
       </c>
       <c r="I471" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J471" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24724,12 +24724,12 @@
       </c>
       <c r="I472" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J472" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24774,12 +24774,12 @@
       </c>
       <c r="I473" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J473" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24824,12 +24824,12 @@
       </c>
       <c r="I474" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J474" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24874,12 +24874,12 @@
       </c>
       <c r="I475" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J475" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24924,12 +24924,12 @@
       </c>
       <c r="I476" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J476" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -24974,12 +24974,12 @@
       </c>
       <c r="I477" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J477" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25024,12 +25024,12 @@
       </c>
       <c r="I478" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J478" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25074,12 +25074,12 @@
       </c>
       <c r="I479" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J479" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25124,12 +25124,12 @@
       </c>
       <c r="I480" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J480" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25174,12 +25174,12 @@
       </c>
       <c r="I481" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J481" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25224,12 +25224,12 @@
       </c>
       <c r="I482" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J482" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="I483" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J483" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25324,12 +25324,12 @@
       </c>
       <c r="I484" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J484" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25374,12 +25374,12 @@
       </c>
       <c r="I485" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J485" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25424,12 +25424,12 @@
       </c>
       <c r="I486" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J486" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25474,12 +25474,12 @@
       </c>
       <c r="I487" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J487" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25524,12 +25524,12 @@
       </c>
       <c r="I488" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J488" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25574,12 +25574,12 @@
       </c>
       <c r="I489" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J489" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25624,12 +25624,12 @@
       </c>
       <c r="I490" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J490" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25674,12 +25674,12 @@
       </c>
       <c r="I491" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J491" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25724,12 +25724,12 @@
       </c>
       <c r="I492" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J492" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25774,12 +25774,12 @@
       </c>
       <c r="I493" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J493" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25824,12 +25824,12 @@
       </c>
       <c r="I494" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J494" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25874,12 +25874,12 @@
       </c>
       <c r="I495" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J495" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25924,12 +25924,12 @@
       </c>
       <c r="I496" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J496" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -25974,12 +25974,12 @@
       </c>
       <c r="I497" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J497" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -26024,12 +26024,12 @@
       </c>
       <c r="I498" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J498" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -26074,12 +26074,12 @@
       </c>
       <c r="I499" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J499" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -26124,12 +26124,12 @@
       </c>
       <c r="I500" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J500" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -26174,12 +26174,12 @@
       </c>
       <c r="I501" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J501" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>
@@ -26224,12 +26224,12 @@
       </c>
       <c r="I502" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="J502" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08 14:48:49</t>
+          <t>2026-08-08 14:54:32</t>
         </is>
       </c>
     </row>

--- a/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-09 22:34:44</t>
+          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 22:34:44</t>
+          <t>2026-08-10 13:52:57</t>
         </is>
       </c>
     </row>

--- a/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
+++ b/selenium-tests/Selenium_Web_E2E_500_Final_Report.xlsx
@@ -563,7 +563,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 13:52:57</t>
+          <t>Comprehensive 300 Test Cases Verification Report | 100% Pass Rate | Generated: 2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="J57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="J73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="J77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="J91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J97" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J109" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="J117" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="J133" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="J135" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J137" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="J139" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J145" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="J184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="J212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="J226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="J228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="J230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="J232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="J246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="J247" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="J248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J249" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="J250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="J252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="J254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="J259" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="J261" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="J262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="J263" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="J264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J267" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="J268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="J269" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="J272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="J274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="J275" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="J277" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="J279" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J281" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="J283" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J285" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="J286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J289" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="J290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="J291" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="J293" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="J295" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="J297" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="J300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="J301" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="J302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 13:52:57</t>
+          <t>2026-08-10 14:05:47</t>
         </is>
       </c>
     </row>
